--- a/artfynd/A 51646-2019 artfynd.xlsx
+++ b/artfynd/A 51646-2019 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 51646-2019 artfynd.xlsx
+++ b/artfynd/A 51646-2019 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY13"/>
+  <dimension ref="A1:AY12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2071,139 +2071,6 @@
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
-    <row r="13">
-      <c r="A13" t="n">
-        <v>112486878</v>
-      </c>
-      <c r="B13" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>VU</t>
-        </is>
-      </c>
-      <c r="E13" t="n">
-        <v>220787</v>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>Goodyera repens</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>101</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
-      <c r="P13" t="inlineStr">
-        <is>
-          <t>Hyltåkra, Sm</t>
-        </is>
-      </c>
-      <c r="Q13" t="n">
-        <v>428966</v>
-      </c>
-      <c r="R13" t="n">
-        <v>6274117</v>
-      </c>
-      <c r="S13" t="n">
-        <v>61</v>
-      </c>
-      <c r="T13" t="inlineStr">
-        <is>
-          <t>Kronoberg</t>
-        </is>
-      </c>
-      <c r="U13" t="inlineStr">
-        <is>
-          <t>Ljungby</t>
-        </is>
-      </c>
-      <c r="V13" t="inlineStr">
-        <is>
-          <t>Småland</t>
-        </is>
-      </c>
-      <c r="W13" t="inlineStr">
-        <is>
-          <t>Hamneda</t>
-        </is>
-      </c>
-      <c r="X13" t="inlineStr">
-        <is>
-          <t>G-Lju-1388</t>
-        </is>
-      </c>
-      <c r="Y13" t="inlineStr">
-        <is>
-          <t>2023-10-02</t>
-        </is>
-      </c>
-      <c r="AA13" t="inlineStr">
-        <is>
-          <t>2023-10-02</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>1 blommsamling. Skogen orörd.</t>
-        </is>
-      </c>
-      <c r="AD13" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE13" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF13" t="inlineStr"/>
-      <c r="AG13" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT13" t="inlineStr"/>
-      <c r="AW13" t="inlineStr">
-        <is>
-          <t>Krister Wahlström</t>
-        </is>
-      </c>
-      <c r="AX13" t="inlineStr">
-        <is>
-          <t>Krister Wahlström</t>
-        </is>
-      </c>
-      <c r="AY13" t="inlineStr">
-        <is>
-          <t>Floraväkteri Sverige</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
